--- a/docs/CodeSystem-BRFabricantePNI.xlsx
+++ b/docs/CodeSystem-BRFabricantePNI.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="326">
   <si>
     <t>Property</t>
   </si>
@@ -940,6 +940,57 @@
   </si>
   <si>
     <t>PFIZER IRELAND PHARMACEUTICALS</t>
+  </si>
+  <si>
+    <t>45240</t>
+  </si>
+  <si>
+    <t>TAKEDA-JAPAO</t>
+  </si>
+  <si>
+    <t>TAKEDA GMBH</t>
+  </si>
+  <si>
+    <t>44329</t>
+  </si>
+  <si>
+    <t>PATHEON</t>
+  </si>
+  <si>
+    <t>PATHEON MANUFATURING SERVICES LLC</t>
+  </si>
+  <si>
+    <t>45686</t>
+  </si>
+  <si>
+    <t>CORIXA-GSK</t>
+  </si>
+  <si>
+    <t>CORIXA CORPORATION DBA GLAXOSMITHKLINE VACCINES</t>
+  </si>
+  <si>
+    <t>45915</t>
+  </si>
+  <si>
+    <t>SINOVAC (DALIAN) VACCINE TECHNOLOGY CO., LTD.</t>
+  </si>
+  <si>
+    <t>46263</t>
+  </si>
+  <si>
+    <t>JIANGSU-DESA</t>
+  </si>
+  <si>
+    <t>JIANGSU DESANO PHARMACEUTICAL CO. LTD.</t>
+  </si>
+  <si>
+    <t>47619</t>
+  </si>
+  <si>
+    <t>LIBBS</t>
+  </si>
+  <si>
+    <t>LIBBS FARMACEUTICA LTDA.</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2538,6 +2589,90 @@
         <v>308</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="D93" t="s" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="D94" t="s" s="2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="D95" t="s" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="D98" t="s" s="2">
+        <v>325</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
